--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/180.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/180.xlsx
@@ -426,13 +426,13 @@
         <v>-4.289543352511234</v>
       </c>
       <c r="E2">
-        <v>-28.58179182624762</v>
+        <v>-30.26241721387027</v>
       </c>
       <c r="F2">
-        <v>-0.8648394817150378</v>
+        <v>-1.8510970916727</v>
       </c>
       <c r="G2">
-        <v>-20.2014962713151</v>
+        <v>-22.23795849652453</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.462473082068628</v>
       </c>
       <c r="E3">
-        <v>-30.1639002618334</v>
+        <v>-28.25314688208896</v>
       </c>
       <c r="F3">
-        <v>-0.9713840890291843</v>
+        <v>-2.285205928300849</v>
       </c>
       <c r="G3">
-        <v>-19.92473135368649</v>
+        <v>-20.85697766699971</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.636472354094556</v>
       </c>
       <c r="E4">
-        <v>-30.22562562679495</v>
+        <v>-32.6540333988302</v>
       </c>
       <c r="F4">
-        <v>-1.188903720955919</v>
+        <v>-2.526752754523674</v>
       </c>
       <c r="G4">
-        <v>-19.40757779281478</v>
+        <v>-22.04363278391485</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.768920737881392</v>
       </c>
       <c r="E5">
-        <v>-28.81261267489258</v>
+        <v>-31.10396844532269</v>
       </c>
       <c r="F5">
-        <v>-1.048074256131382</v>
+        <v>-1.999035812351645</v>
       </c>
       <c r="G5">
-        <v>-19.5534602925483</v>
+        <v>-20.52643790290395</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.843800241320159</v>
       </c>
       <c r="E6">
-        <v>-30.23252702118264</v>
+        <v>-32.1726271767338</v>
       </c>
       <c r="F6">
-        <v>-0.9098452364199959</v>
+        <v>-2.221411878468075</v>
       </c>
       <c r="G6">
-        <v>-19.41800435599071</v>
+        <v>-21.79538490556152</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.846238920921346</v>
       </c>
       <c r="E7">
-        <v>-31.07241630267425</v>
+        <v>-32.74382171721729</v>
       </c>
       <c r="F7">
-        <v>-0.8184155183628035</v>
+        <v>-2.158804024365965</v>
       </c>
       <c r="G7">
-        <v>-19.43804639868546</v>
+        <v>-20.76374608352276</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.765065543320581</v>
       </c>
       <c r="E8">
-        <v>-31.55316589603955</v>
+        <v>-32.943790072448</v>
       </c>
       <c r="F8">
-        <v>-0.9144039338975885</v>
+        <v>-1.837559573507524</v>
       </c>
       <c r="G8">
-        <v>-18.60269478748839</v>
+        <v>-19.31918953746177</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.605305490692092</v>
       </c>
       <c r="E9">
-        <v>-31.95671180028507</v>
+        <v>-35.20293707149855</v>
       </c>
       <c r="F9">
-        <v>-0.715588660685151</v>
+        <v>-1.583967871944824</v>
       </c>
       <c r="G9">
-        <v>-18.29211595772167</v>
+        <v>-19.71533934832759</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.374151685420896</v>
       </c>
       <c r="E10">
-        <v>-33.10946429401861</v>
+        <v>-33.90485678991086</v>
       </c>
       <c r="F10">
-        <v>-0.9109886720909433</v>
+        <v>-1.775446627503988</v>
       </c>
       <c r="G10">
-        <v>-17.69016277286152</v>
+        <v>-18.72495654479922</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.091512031601885</v>
       </c>
       <c r="E11">
-        <v>-33.09349915890457</v>
+        <v>-36.43597261667708</v>
       </c>
       <c r="F11">
-        <v>-0.01473306930770483</v>
+        <v>-2.00392708807148</v>
       </c>
       <c r="G11">
-        <v>-17.28763188546877</v>
+        <v>-19.48994582110461</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.785221295962471</v>
       </c>
       <c r="E12">
-        <v>-32.64521872417427</v>
+        <v>-34.7211481933485</v>
       </c>
       <c r="F12">
-        <v>-0.2644201439358881</v>
+        <v>-1.734301947820872</v>
       </c>
       <c r="G12">
-        <v>-16.77521737053653</v>
+        <v>-18.17594063838479</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.478460875420273</v>
       </c>
       <c r="E13">
-        <v>-35.02338760556843</v>
+        <v>-35.77554449587244</v>
       </c>
       <c r="F13">
-        <v>-0.2507978975042357</v>
+        <v>-1.229916953048055</v>
       </c>
       <c r="G13">
-        <v>-16.35094613058738</v>
+        <v>-18.56926324336006</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.20197266779579</v>
       </c>
       <c r="E14">
-        <v>-34.99628468863252</v>
+        <v>-34.57434865144184</v>
       </c>
       <c r="F14">
-        <v>-0.1705594372984961</v>
+        <v>-1.658567547238642</v>
       </c>
       <c r="G14">
-        <v>-15.53306923401936</v>
+        <v>-18.4930346217728</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.968194993255751</v>
       </c>
       <c r="E15">
-        <v>-34.94256566571654</v>
+        <v>-37.38617778923254</v>
       </c>
       <c r="F15">
-        <v>-0.3888337050939379</v>
+        <v>-1.903221604467559</v>
       </c>
       <c r="G15">
-        <v>-15.01178411231464</v>
+        <v>-17.33049186329294</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.786185375538301</v>
       </c>
       <c r="E16">
-        <v>-36.10822431037193</v>
+        <v>-38.86204369612437</v>
       </c>
       <c r="F16">
-        <v>0.07947842818995701</v>
+        <v>-1.045785801083572</v>
       </c>
       <c r="G16">
-        <v>-15.11609443643876</v>
+        <v>-17.14050958643079</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.655170197459632</v>
       </c>
       <c r="E17">
-        <v>-36.73074457525836</v>
+        <v>-39.06245584180783</v>
       </c>
       <c r="F17">
-        <v>-0.2306484071420996</v>
+        <v>-0.8747257658921684</v>
       </c>
       <c r="G17">
-        <v>-15.07401243681632</v>
+        <v>-15.66196532459088</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.564704282485907</v>
       </c>
       <c r="E18">
-        <v>-38.34457949974188</v>
+        <v>-37.31493130766986</v>
       </c>
       <c r="F18">
-        <v>-0.1772973141157332</v>
+        <v>-1.315673836516143</v>
       </c>
       <c r="G18">
-        <v>-14.3586912752366</v>
+        <v>-16.81831901818507</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.511359484054386</v>
       </c>
       <c r="E19">
-        <v>-38.37994235326779</v>
+        <v>-39.70911060891814</v>
       </c>
       <c r="F19">
-        <v>-0.1507916200619809</v>
+        <v>-0.8644150485297</v>
       </c>
       <c r="G19">
-        <v>-13.91888530034443</v>
+        <v>-16.10282901878285</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.479764675569753</v>
       </c>
       <c r="E20">
-        <v>-40.03593284228871</v>
+        <v>-40.24363583112452</v>
       </c>
       <c r="F20">
-        <v>0.3263053299348567</v>
+        <v>-0.6256587121298798</v>
       </c>
       <c r="G20">
-        <v>-14.68594532288464</v>
+        <v>-16.87863053681951</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.462925549910064</v>
       </c>
       <c r="E21">
-        <v>-39.53945359445777</v>
+        <v>-42.3553221310633</v>
       </c>
       <c r="F21">
-        <v>0.5224441401502014</v>
+        <v>-1.411971866557396</v>
       </c>
       <c r="G21">
-        <v>-14.60719572086923</v>
+        <v>-15.54480677322884</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.451950722461355</v>
       </c>
       <c r="E22">
-        <v>-39.11044860934112</v>
+        <v>-42.05305328376232</v>
       </c>
       <c r="F22">
-        <v>0.190313294829029</v>
+        <v>-1.389154623580702</v>
       </c>
       <c r="G22">
-        <v>-13.18589079140331</v>
+        <v>-15.26591317481848</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.439677971474929</v>
       </c>
       <c r="E23">
-        <v>-40.32062668196593</v>
+        <v>-41.62065647161393</v>
       </c>
       <c r="F23">
-        <v>0.341185038863368</v>
+        <v>-0.8878855701965126</v>
       </c>
       <c r="G23">
-        <v>-13.60647904944002</v>
+        <v>-16.29059488540647</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.432544186044178</v>
       </c>
       <c r="E24">
-        <v>-40.02290895104265</v>
+        <v>-41.97687529400529</v>
       </c>
       <c r="F24">
-        <v>0.4264818557630212</v>
+        <v>-1.039975184079824</v>
       </c>
       <c r="G24">
-        <v>-13.08814693435633</v>
+        <v>-14.61726143458138</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.431827378215996</v>
       </c>
       <c r="E25">
-        <v>-39.79026312737259</v>
+        <v>-41.66348451454147</v>
       </c>
       <c r="F25">
-        <v>0.1127932658271412</v>
+        <v>-0.876176440510711</v>
       </c>
       <c r="G25">
-        <v>-13.21872147151627</v>
+        <v>-15.59321853592238</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.452658365609525</v>
       </c>
       <c r="E26">
-        <v>-40.8885041152388</v>
+        <v>-45.06722822563775</v>
       </c>
       <c r="F26">
-        <v>0.3821452168073362</v>
+        <v>-1.734971855423102</v>
       </c>
       <c r="G26">
-        <v>-13.32376508147734</v>
+        <v>-14.70730661797679</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.505243319170344</v>
       </c>
       <c r="E27">
-        <v>-40.73154720613294</v>
+        <v>-42.8480518024159</v>
       </c>
       <c r="F27">
-        <v>-0.02024278218751867</v>
+        <v>-1.069426571136294</v>
       </c>
       <c r="G27">
-        <v>-13.47838080034346</v>
+        <v>-15.5381476108766</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.597280121713255</v>
       </c>
       <c r="E28">
-        <v>-40.29732994743347</v>
+        <v>-41.64026476406714</v>
       </c>
       <c r="F28">
-        <v>-0.205341578466335</v>
+        <v>-1.879903910421586</v>
       </c>
       <c r="G28">
-        <v>-12.54566438956366</v>
+        <v>-14.39668144057251</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.738102077410918</v>
       </c>
       <c r="E29">
-        <v>-41.48535472521275</v>
+        <v>-41.50184969178569</v>
       </c>
       <c r="F29">
-        <v>-0.301117777408451</v>
+        <v>-1.843279127421133</v>
       </c>
       <c r="G29">
-        <v>-12.63648589588803</v>
+        <v>-15.78254698004052</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.921256369006412</v>
       </c>
       <c r="E30">
-        <v>-38.62026394038084</v>
+        <v>-40.94330544344263</v>
       </c>
       <c r="F30">
-        <v>0.04555544748124405</v>
+        <v>-1.736692551900227</v>
       </c>
       <c r="G30">
-        <v>-13.65462265794487</v>
+        <v>-13.6203866512505</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.146723725664894</v>
       </c>
       <c r="E31">
-        <v>-39.99620453981942</v>
+        <v>-42.8505334061721</v>
       </c>
       <c r="F31">
-        <v>-0.1434313468199761</v>
+        <v>-1.337140178346967</v>
       </c>
       <c r="G31">
-        <v>-14.37533835348083</v>
+        <v>-14.95117298930889</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.402472507922169</v>
       </c>
       <c r="E32">
-        <v>-39.86521163643654</v>
+        <v>-42.22986981562882</v>
       </c>
       <c r="F32">
-        <v>-0.06468236202770729</v>
+        <v>-1.724753784856687</v>
       </c>
       <c r="G32">
-        <v>-12.73802694866855</v>
+        <v>-13.1468164224033</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.675304588244496</v>
       </c>
       <c r="E33">
-        <v>-39.7404974622653</v>
+        <v>-42.5555214384684</v>
       </c>
       <c r="F33">
-        <v>-0.1557224884297016</v>
+        <v>-2.230080292796233</v>
       </c>
       <c r="G33">
-        <v>-13.27868538286909</v>
+        <v>-14.95081213984511</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.955969198143581</v>
       </c>
       <c r="E34">
-        <v>-39.09956442206369</v>
+        <v>-39.74207789969397</v>
       </c>
       <c r="F34">
-        <v>0.4141732933882258</v>
+        <v>-2.270250201488397</v>
       </c>
       <c r="G34">
-        <v>-13.0679459854757</v>
+        <v>-14.98583440110506</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.226531551040341</v>
       </c>
       <c r="E35">
-        <v>-38.38905364297121</v>
+        <v>-41.39909861655165</v>
       </c>
       <c r="F35">
-        <v>0.2316456436631255</v>
+        <v>-1.819772180518265</v>
       </c>
       <c r="G35">
-        <v>-13.82264608624504</v>
+        <v>-15.55019468609401</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.484425768107056</v>
       </c>
       <c r="E36">
-        <v>-37.60012101525092</v>
+        <v>-41.89810475287887</v>
       </c>
       <c r="F36">
-        <v>-0.1589009862019886</v>
+        <v>-1.5246153253519</v>
       </c>
       <c r="G36">
-        <v>-13.43719099274385</v>
+        <v>-15.07447922373735</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.721363446321794</v>
       </c>
       <c r="E37">
-        <v>-38.95085159988879</v>
+        <v>-40.80530246229587</v>
       </c>
       <c r="F37">
-        <v>-0.09314393288702731</v>
+        <v>-1.623594569507993</v>
       </c>
       <c r="G37">
-        <v>-13.89335768369111</v>
+        <v>-15.2709054774917</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.936455288337257</v>
       </c>
       <c r="E38">
-        <v>-37.77122034868272</v>
+        <v>-40.37718505808473</v>
       </c>
       <c r="F38">
-        <v>0.2334178105825022</v>
+        <v>-1.446262267038491</v>
       </c>
       <c r="G38">
-        <v>-13.97097673440486</v>
+        <v>-15.10494120851696</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.135526071777688</v>
       </c>
       <c r="E39">
-        <v>-37.11277796373045</v>
+        <v>-40.04712723003567</v>
       </c>
       <c r="F39">
-        <v>-0.04924598046991899</v>
+        <v>-1.003218161635433</v>
       </c>
       <c r="G39">
-        <v>-13.3587376845542</v>
+        <v>-15.37365487939406</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.31649725894744</v>
       </c>
       <c r="E40">
-        <v>-36.57515073682882</v>
+        <v>-38.04675987815344</v>
       </c>
       <c r="F40">
-        <v>-0.06393722839449302</v>
+        <v>-0.5945531442447336</v>
       </c>
       <c r="G40">
-        <v>-13.80058295549857</v>
+        <v>-16.35544019615694</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.492915332161919</v>
       </c>
       <c r="E41">
-        <v>-37.03408440666216</v>
+        <v>-38.44147752232102</v>
       </c>
       <c r="F41">
-        <v>0.1155885067678919</v>
+        <v>-1.654025478673161</v>
       </c>
       <c r="G41">
-        <v>-14.55317092821386</v>
+        <v>-17.15373190531464</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.665620115812835</v>
       </c>
       <c r="E42">
-        <v>-35.98255915665908</v>
+        <v>-36.84107178750723</v>
       </c>
       <c r="F42">
-        <v>0.2986173994152288</v>
+        <v>-1.411109538686439</v>
       </c>
       <c r="G42">
-        <v>-13.50963566077972</v>
+        <v>-16.61350549730698</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.841185244851272</v>
       </c>
       <c r="E43">
-        <v>-35.05903575295681</v>
+        <v>-37.27152135583233</v>
       </c>
       <c r="F43">
-        <v>0.4008978785520546</v>
+        <v>-1.146207009475672</v>
       </c>
       <c r="G43">
-        <v>-14.64210873412638</v>
+        <v>-14.55123591434616</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.025977347348834</v>
       </c>
       <c r="E44">
-        <v>-34.83589066775485</v>
+        <v>-36.92164466128871</v>
       </c>
       <c r="F44">
-        <v>-0.0394262119412367</v>
+        <v>-1.13242480874656</v>
       </c>
       <c r="G44">
-        <v>-15.16595787335127</v>
+        <v>-16.52696783691043</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.213933847664817</v>
       </c>
       <c r="E45">
-        <v>-33.06201267912924</v>
+        <v>-37.43581439283061</v>
       </c>
       <c r="F45">
-        <v>0.3350180880286468</v>
+        <v>-1.212092342969784</v>
       </c>
       <c r="G45">
-        <v>-14.44101957697997</v>
+        <v>-15.82329814035618</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.414455711979308</v>
       </c>
       <c r="E46">
-        <v>-33.49573406992488</v>
+        <v>-36.68334956629408</v>
       </c>
       <c r="F46">
-        <v>0.5549085277107946</v>
+        <v>-1.113114682519607</v>
       </c>
       <c r="G46">
-        <v>-14.86584036748864</v>
+        <v>-15.18925087176558</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.618979896373364</v>
       </c>
       <c r="E47">
-        <v>-33.65425103832638</v>
+        <v>-36.58987733430176</v>
       </c>
       <c r="F47">
-        <v>0.3573911014960598</v>
+        <v>-1.217929882974093</v>
       </c>
       <c r="G47">
-        <v>-14.94400565821637</v>
+        <v>-16.71142481326754</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.829398732816203</v>
       </c>
       <c r="E48">
-        <v>-34.00369073512826</v>
+        <v>-34.84189995276302</v>
       </c>
       <c r="F48">
-        <v>0.1907052620431003</v>
+        <v>-1.036521121478251</v>
       </c>
       <c r="G48">
-        <v>-15.22246391988832</v>
+        <v>-18.31731251982106</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.04491742612719</v>
       </c>
       <c r="E49">
-        <v>-32.6496022870137</v>
+        <v>-36.34505444402508</v>
       </c>
       <c r="F49">
-        <v>0.6468584931612089</v>
+        <v>-0.9461904953263736</v>
       </c>
       <c r="G49">
-        <v>-14.90606018524524</v>
+        <v>-16.62113464950223</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.254931105808028</v>
       </c>
       <c r="E50">
-        <v>-32.81424628074758</v>
+        <v>-33.72895274555691</v>
       </c>
       <c r="F50">
-        <v>0.4681570769278102</v>
+        <v>-1.551819433714361</v>
       </c>
       <c r="G50">
-        <v>-15.3668169475827</v>
+        <v>-17.81180545815651</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.466593258447512</v>
       </c>
       <c r="E51">
-        <v>-32.05716467496023</v>
+        <v>-32.35280383631398</v>
       </c>
       <c r="F51">
-        <v>0.1432661431990694</v>
+        <v>-1.165445077083472</v>
       </c>
       <c r="G51">
-        <v>-15.73134608273016</v>
+        <v>-17.87791208675744</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.667346903231427</v>
       </c>
       <c r="E52">
-        <v>-30.22545580901966</v>
+        <v>-31.72135794915843</v>
       </c>
       <c r="F52">
-        <v>0.6262402258481027</v>
+        <v>-1.285086932318303</v>
       </c>
       <c r="G52">
-        <v>-14.90358886300018</v>
+        <v>-17.29191738666936</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.861054403133168</v>
       </c>
       <c r="E53">
-        <v>-31.58204623902347</v>
+        <v>-32.78239073034062</v>
       </c>
       <c r="F53">
-        <v>0.5217124680172683</v>
+        <v>-1.462557017202448</v>
       </c>
       <c r="G53">
-        <v>-15.62337098469406</v>
+        <v>-17.43025184257334</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.045417207693641</v>
       </c>
       <c r="E54">
-        <v>-31.20338656368709</v>
+        <v>-32.99489843009857</v>
       </c>
       <c r="F54">
-        <v>0.3938440524046873</v>
+        <v>-1.807737599266841</v>
       </c>
       <c r="G54">
-        <v>-17.05091960304703</v>
+        <v>-17.59975011891126</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.212077335867631</v>
       </c>
       <c r="E55">
-        <v>-30.01540480641088</v>
+        <v>-31.97484381021179</v>
       </c>
       <c r="F55">
-        <v>0.1527992609570571</v>
+        <v>-1.092505125589035</v>
       </c>
       <c r="G55">
-        <v>-16.24343616419955</v>
+        <v>-17.51534610511477</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.369274108712464</v>
       </c>
       <c r="E56">
-        <v>-28.83543618389124</v>
+        <v>-31.05111436094217</v>
       </c>
       <c r="F56">
-        <v>0.3010998584376801</v>
+        <v>-1.098353751534753</v>
       </c>
       <c r="G56">
-        <v>-16.3280603292744</v>
+        <v>-17.85747112332521</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.503712105463993</v>
       </c>
       <c r="E57">
-        <v>-28.40429828751698</v>
+        <v>-28.75908611212192</v>
       </c>
       <c r="F57">
-        <v>0.4858684520331273</v>
+        <v>-1.326325842503389</v>
       </c>
       <c r="G57">
-        <v>-16.29805519977922</v>
+        <v>-18.13618760754922</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.623390078587592</v>
       </c>
       <c r="E58">
-        <v>-28.07894101548789</v>
+        <v>-30.22389801396103</v>
       </c>
       <c r="F58">
-        <v>0.5108514128491846</v>
+        <v>-1.308313563274138</v>
       </c>
       <c r="G58">
-        <v>-16.27404050243734</v>
+        <v>-17.8265026250781</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.72597273417089</v>
       </c>
       <c r="E59">
-        <v>-28.79262399062272</v>
+        <v>-29.54429406997091</v>
       </c>
       <c r="F59">
-        <v>0.3333045182281413</v>
+        <v>-1.152849072085025</v>
       </c>
       <c r="G59">
-        <v>-16.23259743810398</v>
+        <v>-19.64051770859452</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.807438793511537</v>
       </c>
       <c r="E60">
-        <v>-28.56908039970808</v>
+        <v>-30.30036809029155</v>
       </c>
       <c r="F60">
-        <v>0.3927156619399367</v>
+        <v>-0.6495679203352691</v>
       </c>
       <c r="G60">
-        <v>-16.15890966021811</v>
+        <v>-18.28008874577749</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.879587069728004</v>
       </c>
       <c r="E61">
-        <v>-28.64756791120903</v>
+        <v>-30.64747788721649</v>
       </c>
       <c r="F61">
-        <v>0.3400843632521376</v>
+        <v>-0.8794950962565143</v>
       </c>
       <c r="G61">
-        <v>-16.95438243984912</v>
+        <v>-18.59332759888502</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.931734414271311</v>
       </c>
       <c r="E62">
-        <v>-27.62343540047835</v>
+        <v>-28.44401753303825</v>
       </c>
       <c r="F62">
-        <v>0.6932927506018934</v>
+        <v>-1.732234419748265</v>
       </c>
       <c r="G62">
-        <v>-16.98467227626068</v>
+        <v>-18.7266200939327</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.979344519649727</v>
       </c>
       <c r="E63">
-        <v>-27.42767852607477</v>
+        <v>-28.77992162103121</v>
       </c>
       <c r="F63">
-        <v>-0.0941028668188259</v>
+        <v>-0.6383727032190276</v>
       </c>
       <c r="G63">
-        <v>-17.1073594386733</v>
+        <v>-19.42007179167999</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.022267002128197</v>
       </c>
       <c r="E64">
-        <v>-26.70799985135378</v>
+        <v>-30.56473361014833</v>
       </c>
       <c r="F64">
-        <v>0.0447224181697229</v>
+        <v>-1.490246531427991</v>
       </c>
       <c r="G64">
-        <v>-17.46275312340514</v>
+        <v>-19.5175359076289</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.062364303257066</v>
       </c>
       <c r="E65">
-        <v>-26.77328686112236</v>
+        <v>-29.80184197220914</v>
       </c>
       <c r="F65">
-        <v>0.2276246143438247</v>
+        <v>-1.275360602438632</v>
       </c>
       <c r="G65">
-        <v>-17.32326659765349</v>
+        <v>-17.90244157393067</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.113797798538682</v>
       </c>
       <c r="E66">
-        <v>-26.88233704370107</v>
+        <v>-29.76543756966148</v>
       </c>
       <c r="F66">
-        <v>-0.06553360395725599</v>
+        <v>-1.891163267627403</v>
       </c>
       <c r="G66">
-        <v>-16.91595859304756</v>
+        <v>-18.94679289084024</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.16655686278116</v>
       </c>
       <c r="E67">
-        <v>-27.66404675537913</v>
+        <v>-29.98872077332068</v>
       </c>
       <c r="F67">
-        <v>-0.04409814439178306</v>
+        <v>-2.087949813562162</v>
       </c>
       <c r="G67">
-        <v>-17.0619222011468</v>
+        <v>-19.59151997934053</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.237395821417774</v>
       </c>
       <c r="E68">
-        <v>-26.31335692700733</v>
+        <v>-28.77227755690626</v>
       </c>
       <c r="F68">
-        <v>0.11415842032625</v>
+        <v>-1.906521255742377</v>
       </c>
       <c r="G68">
-        <v>-16.27874147710311</v>
+        <v>-17.92210786970671</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.321264241080506</v>
       </c>
       <c r="E69">
-        <v>-26.95081209917105</v>
+        <v>-29.63385370042061</v>
       </c>
       <c r="F69">
-        <v>-0.2494596660056894</v>
+        <v>-0.9353919965419497</v>
       </c>
       <c r="G69">
-        <v>-17.88226379886881</v>
+        <v>-20.55480100181166</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.418218965151549</v>
       </c>
       <c r="E70">
-        <v>-27.36046238637892</v>
+        <v>-29.49990823198473</v>
       </c>
       <c r="F70">
-        <v>-0.08044577885703383</v>
+        <v>-1.674234358007126</v>
       </c>
       <c r="G70">
-        <v>-17.61106390829172</v>
+        <v>-17.45400831736315</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.534464079315343</v>
       </c>
       <c r="E71">
-        <v>-26.86373860095157</v>
+        <v>-29.32125540390812</v>
       </c>
       <c r="F71">
-        <v>-0.3570099265761399</v>
+        <v>-1.468044558199445</v>
       </c>
       <c r="G71">
-        <v>-16.87677497604475</v>
+        <v>-18.22540846510535</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.653082903847102</v>
       </c>
       <c r="E72">
-        <v>-26.51937985198629</v>
+        <v>-27.98102182202003</v>
       </c>
       <c r="F72">
-        <v>0.01025543447905649</v>
+        <v>-1.159798373641973</v>
       </c>
       <c r="G72">
-        <v>-17.31662729857448</v>
+        <v>-18.85752237510102</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.783475579833246</v>
       </c>
       <c r="E73">
-        <v>-27.032252175725</v>
+        <v>-28.68985480149265</v>
       </c>
       <c r="F73">
-        <v>-0.2163641716377935</v>
+        <v>-1.195571914712877</v>
       </c>
       <c r="G73">
-        <v>-16.67900629607423</v>
+        <v>-20.40649187219785</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.91025682583961</v>
       </c>
       <c r="E74">
-        <v>-26.47789450160202</v>
+        <v>-27.92023611541507</v>
       </c>
       <c r="F74">
-        <v>-0.3465923090643793</v>
+        <v>-1.902157354092383</v>
       </c>
       <c r="G74">
-        <v>-18.05504117056338</v>
+        <v>-19.54555139925498</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.02795050878028</v>
       </c>
       <c r="E75">
-        <v>-27.60322934945612</v>
+        <v>-31.84400940341918</v>
       </c>
       <c r="F75">
-        <v>-0.4630572502328385</v>
+        <v>-2.054764047957086</v>
       </c>
       <c r="G75">
-        <v>-17.13575233249086</v>
+        <v>-18.59423137781724</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.13335788740838</v>
       </c>
       <c r="E76">
-        <v>-26.36829184519437</v>
+        <v>-29.7681614467771</v>
       </c>
       <c r="F76">
-        <v>-0.2391536997609672</v>
+        <v>-1.373636681168269</v>
       </c>
       <c r="G76">
-        <v>-16.99526767725911</v>
+        <v>-16.96973675006026</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.20485631969947</v>
       </c>
       <c r="E77">
-        <v>-27.07814825979273</v>
+        <v>-29.68242384838987</v>
       </c>
       <c r="F77">
-        <v>-1.030692291856476</v>
+        <v>-2.275268965534424</v>
       </c>
       <c r="G77">
-        <v>-16.2692948354068</v>
+        <v>-17.69955479055644</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.24716318672662</v>
       </c>
       <c r="E78">
-        <v>-26.53244902797243</v>
+        <v>-27.67472489708922</v>
       </c>
       <c r="F78">
-        <v>-0.430534265553374</v>
+        <v>-2.038651423973405</v>
       </c>
       <c r="G78">
-        <v>-15.60401919074425</v>
+        <v>-18.88141954807625</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.24179088788108</v>
       </c>
       <c r="E79">
-        <v>-28.21035280271647</v>
+        <v>-32.44441486548915</v>
       </c>
       <c r="F79">
-        <v>-1.027386305757996</v>
+        <v>-2.041083204406562</v>
       </c>
       <c r="G79">
-        <v>-16.17978099457044</v>
+        <v>-17.60325433136458</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.18616192516587</v>
       </c>
       <c r="E80">
-        <v>-28.46209972975088</v>
+        <v>-30.76472234351208</v>
       </c>
       <c r="F80">
-        <v>-0.911740932400777</v>
+        <v>-2.178897293168103</v>
       </c>
       <c r="G80">
-        <v>-16.03469633631188</v>
+        <v>-18.67620214064237</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.07920966248096</v>
       </c>
       <c r="E81">
-        <v>-27.99088483840873</v>
+        <v>-27.65963149322165</v>
       </c>
       <c r="F81">
-        <v>-0.7872331407407585</v>
+        <v>-1.758253916085978</v>
       </c>
       <c r="G81">
-        <v>-15.14730625978301</v>
+        <v>-18.03107944195013</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.909636566401071</v>
       </c>
       <c r="E82">
-        <v>-28.77315155238974</v>
+        <v>-29.75844560579364</v>
       </c>
       <c r="F82">
-        <v>-0.446581957594522</v>
+        <v>-2.259357472202004</v>
       </c>
       <c r="G82">
-        <v>-15.49170231223339</v>
+        <v>-16.52918093660343</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.692868146917833</v>
       </c>
       <c r="E83">
-        <v>-28.49820525301404</v>
+        <v>-30.32325726216332</v>
       </c>
       <c r="F83">
-        <v>-1.045890325673991</v>
+        <v>-1.643616571543936</v>
       </c>
       <c r="G83">
-        <v>-15.77177446485573</v>
+        <v>-17.41579303493058</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.423355289430299</v>
       </c>
       <c r="E84">
-        <v>-30.6791273920561</v>
+        <v>-30.23027184112682</v>
       </c>
       <c r="F84">
-        <v>-1.052215647100256</v>
+        <v>-2.010372771147318</v>
       </c>
       <c r="G84">
-        <v>-15.91820651514878</v>
+        <v>-16.68027423501577</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.115698955183912</v>
       </c>
       <c r="E85">
-        <v>-30.87567448517401</v>
+        <v>-33.40028968750222</v>
       </c>
       <c r="F85">
-        <v>-0.7882506717914284</v>
+        <v>-2.322126072454531</v>
       </c>
       <c r="G85">
-        <v>-15.37148481679307</v>
+        <v>-18.96204291886689</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.782042222158573</v>
       </c>
       <c r="E86">
-        <v>-32.21287625371397</v>
+        <v>-33.86590285649687</v>
       </c>
       <c r="F86">
-        <v>-1.144397625467282</v>
+        <v>-1.815878639525158</v>
       </c>
       <c r="G86">
-        <v>-15.93135103621245</v>
+        <v>-17.51437280472623</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.428043270048327</v>
       </c>
       <c r="E87">
-        <v>-32.07446797414353</v>
+        <v>-34.50621323152244</v>
       </c>
       <c r="F87">
-        <v>-1.064492535356742</v>
+        <v>-2.515112516045194</v>
       </c>
       <c r="G87">
-        <v>-15.33056481865491</v>
+        <v>-16.36821890193853</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.081928706696656</v>
       </c>
       <c r="E88">
-        <v>-32.27820628398563</v>
+        <v>-32.65930227833812</v>
       </c>
       <c r="F88">
-        <v>-1.264101245232815</v>
+        <v>-2.445302759292623</v>
       </c>
       <c r="G88">
-        <v>-14.677377631029</v>
+        <v>-16.52700590818413</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.747576704235065</v>
       </c>
       <c r="E89">
-        <v>-34.39316893486896</v>
+        <v>-36.30832172711186</v>
       </c>
       <c r="F89">
-        <v>-1.177849453666152</v>
+        <v>-3.19912935427673</v>
       </c>
       <c r="G89">
-        <v>-14.97962878349169</v>
+        <v>-15.87985384507632</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.45022563286909</v>
       </c>
       <c r="E90">
-        <v>-34.41309422050271</v>
+        <v>-35.9591922307795</v>
       </c>
       <c r="F90">
-        <v>-1.215445840245727</v>
+        <v>-2.843120183015519</v>
       </c>
       <c r="G90">
-        <v>-14.26865767875059</v>
+        <v>-16.32446838736429</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.202808578462468</v>
       </c>
       <c r="E91">
-        <v>-36.98500706960403</v>
+        <v>-36.16956475504283</v>
       </c>
       <c r="F91">
-        <v>-1.305714701866902</v>
+        <v>-2.177082366189009</v>
       </c>
       <c r="G91">
-        <v>-14.13322657128454</v>
+        <v>-16.9880672407112</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.010791696833401</v>
       </c>
       <c r="E92">
-        <v>-36.82609838820088</v>
+        <v>-38.65171419236411</v>
       </c>
       <c r="F92">
-        <v>-1.319503237419676</v>
+        <v>-2.660044571043677</v>
       </c>
       <c r="G92">
-        <v>-15.00629357253776</v>
+        <v>-16.8396869343683</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.894113767568404</v>
       </c>
       <c r="E93">
-        <v>-38.5792042665533</v>
+        <v>-39.36378050227822</v>
       </c>
       <c r="F93">
-        <v>-1.304789817612285</v>
+        <v>-2.98227804624631</v>
       </c>
       <c r="G93">
-        <v>-15.08834875427413</v>
+        <v>-16.12757865723444</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.842274270510476</v>
       </c>
       <c r="E94">
-        <v>-39.72838605853178</v>
+        <v>-40.96753051514666</v>
       </c>
       <c r="F94">
-        <v>-1.672657778768307</v>
+        <v>-3.256688353920419</v>
       </c>
       <c r="G94">
-        <v>-13.68358165504965</v>
+        <v>-15.99765629754575</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.86511324258921</v>
       </c>
       <c r="E95">
-        <v>-41.15037897439137</v>
+        <v>-39.95229872007805</v>
       </c>
       <c r="F95">
-        <v>-1.860499553692664</v>
+        <v>-2.231922934628847</v>
       </c>
       <c r="G95">
-        <v>-13.37957094763284</v>
+        <v>-17.24809900591156</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.956412774320426</v>
       </c>
       <c r="E96">
-        <v>-41.824974426129</v>
+        <v>-44.54091086257027</v>
       </c>
       <c r="F96">
-        <v>-1.707718652177263</v>
+        <v>-3.384194100878364</v>
       </c>
       <c r="G96">
-        <v>-13.76858487758875</v>
+        <v>-14.93242702519277</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.101774143045566</v>
       </c>
       <c r="E97">
-        <v>-43.20367739471226</v>
+        <v>-45.14425983274523</v>
       </c>
       <c r="F97">
-        <v>-2.155618399917059</v>
+        <v>-2.988003143130624</v>
       </c>
       <c r="G97">
-        <v>-13.86624597099724</v>
+        <v>-15.93929965605225</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.312181790735558</v>
       </c>
       <c r="E98">
-        <v>-46.62224959394666</v>
+        <v>-45.34487575975903</v>
       </c>
       <c r="F98">
-        <v>-2.066957791653012</v>
+        <v>-3.721240769361061</v>
       </c>
       <c r="G98">
-        <v>-14.05042155098352</v>
+        <v>-15.97852631014707</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.556386194432792</v>
       </c>
       <c r="E99">
-        <v>-47.90901548322618</v>
+        <v>-48.73317963872616</v>
       </c>
       <c r="F99">
-        <v>-2.374138142129393</v>
+        <v>-2.533738481316677</v>
       </c>
       <c r="G99">
-        <v>-13.44245144960575</v>
+        <v>-16.14690893263825</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.860294627968494</v>
       </c>
       <c r="E100">
-        <v>-49.26670859665086</v>
+        <v>-48.21476219856506</v>
       </c>
       <c r="F100">
-        <v>-2.968966206174084</v>
+        <v>-3.828750645430667</v>
       </c>
       <c r="G100">
-        <v>-14.55530291954115</v>
+        <v>-16.26289389560662</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.182981700298418</v>
       </c>
       <c r="E101">
-        <v>-50.68925285422087</v>
+        <v>-50.74076877453213</v>
       </c>
       <c r="F101">
-        <v>-2.664688788640703</v>
+        <v>-4.143484481270738</v>
       </c>
       <c r="G101">
-        <v>-13.25764024487594</v>
+        <v>-16.15830383038442</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.571209936789311</v>
       </c>
       <c r="E102">
-        <v>-52.92741037624587</v>
+        <v>-54.07169122722956</v>
       </c>
       <c r="F102">
-        <v>-2.731493463418728</v>
+        <v>-3.724108860773922</v>
       </c>
       <c r="G102">
-        <v>-13.66235443705184</v>
+        <v>-15.98351199172921</v>
       </c>
     </row>
   </sheetData>
